--- a/야근계획.xlsx
+++ b/야근계획.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\3F11\Desktop\야근계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{361CEAFF-EC9F-4D90-AA33-8E9CAE71025A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D547703-4BE7-4BF4-9CAA-30CD8B9207A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{33A2A4D5-9034-4DEC-BA66-CA6D43A19B0F}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{33A2A4D5-9034-4DEC-BA66-CA6D43A19B0F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>권회준</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -52,6 +52,14 @@
   </si>
   <si>
     <t>테이</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>라나</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>이르판</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -122,7 +130,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -130,6 +138,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="20" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -446,10 +460,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1FA2FE8D-7579-419F-8920-716C175AB9EF}">
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="31.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -472,8 +486,14 @@
       <c r="H1" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>0.79166666666666663</v>
       </c>
@@ -484,8 +504,10 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I2" s="3"/>
+      <c r="J2" s="3"/>
+    </row>
+    <row r="3" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>0.8125</v>
       </c>
@@ -496,8 +518,10 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-    </row>
-    <row r="4" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I3" s="3"/>
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>0.83333333333333304</v>
       </c>
@@ -508,8 +532,10 @@
       <c r="F4" s="1"/>
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
-    </row>
-    <row r="5" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I4" s="3"/>
+      <c r="J4" s="3"/>
+    </row>
+    <row r="5" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>0.85416666666666696</v>
       </c>
@@ -520,8 +546,10 @@
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
-    </row>
-    <row r="6" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I5" s="3"/>
+      <c r="J5" s="3"/>
+    </row>
+    <row r="6" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>0.875</v>
       </c>
@@ -532,8 +560,10 @@
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
-    </row>
-    <row r="7" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I6" s="3"/>
+      <c r="J6" s="3"/>
+    </row>
+    <row r="7" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>0.89583333333333404</v>
       </c>
@@ -544,8 +574,10 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
-    </row>
-    <row r="8" spans="1:8" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I7" s="3"/>
+      <c r="J7" s="3"/>
+    </row>
+    <row r="8" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>0.91666666666666696</v>
       </c>
@@ -556,6 +588,8 @@
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
